--- a/qry-export-us5.xlsx
+++ b/qry-export-us5.xlsx
@@ -30162,6 +30162,9 @@
       <c r="M426" s="2">
         <v>762.17</v>
       </c>
+      <c r="N426" s="0">
+        <v>1</v>
+      </c>
       <c r="O426" s="0">
         <v>762.17</v>
       </c>
@@ -30215,6 +30218,9 @@
       <c r="M427" s="2">
         <v>570.14</v>
       </c>
+      <c r="N427" s="0">
+        <v>1</v>
+      </c>
       <c r="O427" s="0">
         <v>570.14</v>
       </c>
@@ -30268,6 +30274,9 @@
       <c r="M428" s="2">
         <v>188.35</v>
       </c>
+      <c r="N428" s="0">
+        <v>1</v>
+      </c>
       <c r="O428" s="0">
         <v>188.35</v>
       </c>
@@ -30321,6 +30330,9 @@
       <c r="M429" s="2">
         <v>249.36</v>
       </c>
+      <c r="N429" s="0">
+        <v>1</v>
+      </c>
       <c r="O429" s="0">
         <v>249.36</v>
       </c>
@@ -30374,6 +30386,9 @@
       <c r="M430" s="2">
         <v>156.34</v>
       </c>
+      <c r="N430" s="0">
+        <v>1</v>
+      </c>
       <c r="O430" s="0">
         <v>156.34</v>
       </c>
@@ -30427,6 +30442,9 @@
       <c r="M431" s="2">
         <v>-7.5</v>
       </c>
+      <c r="N431" s="0">
+        <v>1</v>
+      </c>
       <c r="O431" s="0">
         <v>-7.5</v>
       </c>
@@ -30480,8 +30498,11 @@
       <c r="M432" s="2">
         <v>269.36</v>
       </c>
+      <c r="N432" s="0">
+        <v>0.8724</v>
+      </c>
       <c r="O432" s="0">
-        <v>269.36</v>
+        <v>308.76</v>
       </c>
       <c r="P432" s="0">
         <v>0</v>
@@ -30533,6 +30554,9 @@
       <c r="M433" s="2">
         <v>762.17</v>
       </c>
+      <c r="N433" s="0">
+        <v>1</v>
+      </c>
       <c r="O433" s="0">
         <v>762.17</v>
       </c>
@@ -30586,6 +30610,9 @@
       <c r="M434" s="2">
         <v>570.14</v>
       </c>
+      <c r="N434" s="0">
+        <v>1</v>
+      </c>
       <c r="O434" s="0">
         <v>570.14</v>
       </c>
@@ -30639,6 +30666,9 @@
       <c r="M435" s="2">
         <v>188.35</v>
       </c>
+      <c r="N435" s="0">
+        <v>1</v>
+      </c>
       <c r="O435" s="0">
         <v>188.35</v>
       </c>
@@ -30692,6 +30722,9 @@
       <c r="M436" s="2">
         <v>249.37</v>
       </c>
+      <c r="N436" s="0">
+        <v>1</v>
+      </c>
       <c r="O436" s="0">
         <v>249.37</v>
       </c>
@@ -30745,6 +30778,9 @@
       <c r="M437" s="2">
         <v>156.34</v>
       </c>
+      <c r="N437" s="0">
+        <v>1</v>
+      </c>
       <c r="O437" s="0">
         <v>156.34</v>
       </c>
@@ -30798,6 +30834,9 @@
       <c r="M438" s="2">
         <v>169.32</v>
       </c>
+      <c r="N438" s="0">
+        <v>1</v>
+      </c>
       <c r="O438" s="0">
         <v>169.32</v>
       </c>
@@ -30851,6 +30890,9 @@
       <c r="M439" s="2">
         <v>169.33</v>
       </c>
+      <c r="N439" s="0">
+        <v>1</v>
+      </c>
       <c r="O439" s="0">
         <v>169.33</v>
       </c>
@@ -30904,8 +30946,11 @@
       <c r="M440" s="2">
         <v>165.09</v>
       </c>
+      <c r="N440" s="0">
+        <v>24.245</v>
+      </c>
       <c r="O440" s="0">
-        <v>165.09</v>
+        <v>6.81</v>
       </c>
       <c r="P440" s="0">
         <v>0</v>
@@ -30957,6 +31002,9 @@
       <c r="M441" s="2">
         <v>371</v>
       </c>
+      <c r="N441" s="0">
+        <v>1</v>
+      </c>
       <c r="O441" s="0">
         <v>371</v>
       </c>
@@ -31010,6 +31058,9 @@
       <c r="M442" s="2">
         <v>371.01</v>
       </c>
+      <c r="N442" s="0">
+        <v>1</v>
+      </c>
       <c r="O442" s="0">
         <v>371.01</v>
       </c>
@@ -31063,6 +31114,9 @@
       <c r="M443" s="2">
         <v>205.97</v>
       </c>
+      <c r="N443" s="0">
+        <v>1</v>
+      </c>
       <c r="O443" s="0">
         <v>205.97</v>
       </c>
@@ -31116,6 +31170,9 @@
       <c r="M444" s="2">
         <v>205.97</v>
       </c>
+      <c r="N444" s="0">
+        <v>1</v>
+      </c>
       <c r="O444" s="0">
         <v>205.97</v>
       </c>
@@ -31169,8 +31226,11 @@
       <c r="M445" s="2">
         <v>398.3</v>
       </c>
+      <c r="N445" s="0">
+        <v>0.8719</v>
+      </c>
       <c r="O445" s="0">
-        <v>398.3</v>
+        <v>456.82</v>
       </c>
       <c r="P445" s="0">
         <v>0</v>
@@ -31222,6 +31282,9 @@
       <c r="M446" s="2">
         <v>230.06</v>
       </c>
+      <c r="N446" s="0">
+        <v>1</v>
+      </c>
       <c r="O446" s="0">
         <v>230.06</v>
       </c>
@@ -31275,6 +31338,9 @@
       <c r="M447" s="2">
         <v>230.05</v>
       </c>
+      <c r="N447" s="0">
+        <v>1</v>
+      </c>
       <c r="O447" s="0">
         <v>230.05</v>
       </c>
@@ -31328,6 +31394,9 @@
       <c r="M448" s="2">
         <v>214.45</v>
       </c>
+      <c r="N448" s="0">
+        <v>1</v>
+      </c>
       <c r="O448" s="0">
         <v>214.45</v>
       </c>
@@ -31381,6 +31450,9 @@
       <c r="M449" s="2">
         <v>214.45</v>
       </c>
+      <c r="N449" s="0">
+        <v>1</v>
+      </c>
       <c r="O449" s="0">
         <v>214.45</v>
       </c>
@@ -31434,6 +31506,9 @@
       <c r="M450" s="2">
         <v>521.26</v>
       </c>
+      <c r="N450" s="0">
+        <v>1</v>
+      </c>
       <c r="O450" s="0">
         <v>521.26</v>
       </c>
@@ -31487,6 +31562,9 @@
       <c r="M451" s="2">
         <v>114.16</v>
       </c>
+      <c r="N451" s="0">
+        <v>1</v>
+      </c>
       <c r="O451" s="0">
         <v>114.16</v>
       </c>
@@ -31540,6 +31618,9 @@
       <c r="M452" s="2">
         <v>114.16</v>
       </c>
+      <c r="N452" s="0">
+        <v>1</v>
+      </c>
       <c r="O452" s="0">
         <v>114.16</v>
       </c>
@@ -31593,6 +31674,9 @@
       <c r="M453" s="2">
         <v>638.57</v>
       </c>
+      <c r="N453" s="0">
+        <v>1</v>
+      </c>
       <c r="O453" s="0">
         <v>638.57</v>
       </c>
@@ -31646,6 +31730,9 @@
       <c r="M454" s="2">
         <v>638.57</v>
       </c>
+      <c r="N454" s="0">
+        <v>1</v>
+      </c>
       <c r="O454" s="0">
         <v>638.57</v>
       </c>
@@ -31699,6 +31786,9 @@
       <c r="M455" s="2">
         <v>76.22</v>
       </c>
+      <c r="N455" s="0">
+        <v>1</v>
+      </c>
       <c r="O455" s="0">
         <v>76.22</v>
       </c>
@@ -31752,6 +31842,9 @@
       <c r="M456" s="2">
         <v>76.21</v>
       </c>
+      <c r="N456" s="0">
+        <v>1</v>
+      </c>
       <c r="O456" s="0">
         <v>76.21</v>
       </c>
@@ -31805,6 +31898,9 @@
       <c r="M457" s="2">
         <v>195.03</v>
       </c>
+      <c r="N457" s="0">
+        <v>1</v>
+      </c>
       <c r="O457" s="0">
         <v>195.03</v>
       </c>
@@ -31858,6 +31954,9 @@
       <c r="M458" s="2">
         <v>195.03</v>
       </c>
+      <c r="N458" s="0">
+        <v>1</v>
+      </c>
       <c r="O458" s="0">
         <v>195.03</v>
       </c>
@@ -31911,6 +32010,9 @@
       <c r="M459" s="2">
         <v>-7.5</v>
       </c>
+      <c r="N459" s="0">
+        <v>1</v>
+      </c>
       <c r="O459" s="0">
         <v>-7.5</v>
       </c>
@@ -31964,8 +32066,11 @@
       <c r="M460" s="2">
         <v>269.36</v>
       </c>
+      <c r="N460" s="0">
+        <v>0.86693</v>
+      </c>
       <c r="O460" s="0">
-        <v>269.36</v>
+        <v>310.71</v>
       </c>
       <c r="P460" s="0">
         <v>0</v>
@@ -32017,8 +32122,11 @@
       <c r="M461" s="2">
         <v>165.09</v>
       </c>
+      <c r="N461" s="0">
+        <v>24.467</v>
+      </c>
       <c r="O461" s="0">
-        <v>165.09</v>
+        <v>6.75</v>
       </c>
       <c r="P461" s="0">
         <v>0</v>
@@ -32070,8 +32178,11 @@
       <c r="M462" s="2">
         <v>398.3</v>
       </c>
+      <c r="N462" s="0">
+        <v>0.86541</v>
+      </c>
       <c r="O462" s="0">
-        <v>398.3</v>
+        <v>460.24</v>
       </c>
       <c r="P462" s="0">
         <v>0</v>
@@ -32123,6 +32234,9 @@
       <c r="M463" s="2">
         <v>521.26</v>
       </c>
+      <c r="N463" s="0">
+        <v>1</v>
+      </c>
       <c r="O463" s="0">
         <v>521.26</v>
       </c>
@@ -32176,6 +32290,9 @@
       <c r="M464" s="2">
         <v>83.62</v>
       </c>
+      <c r="N464" s="0">
+        <v>1</v>
+      </c>
       <c r="O464" s="0">
         <v>83.62</v>
       </c>
@@ -32229,6 +32346,9 @@
       <c r="M465" s="2">
         <v>-7.5</v>
       </c>
+      <c r="N465" s="0">
+        <v>1</v>
+      </c>
       <c r="O465" s="0">
         <v>-7.5</v>
       </c>
@@ -32282,6 +32402,9 @@
       <c r="M466" s="2">
         <v>83.62</v>
       </c>
+      <c r="N466" s="0">
+        <v>1</v>
+      </c>
       <c r="O466" s="0">
         <v>83.62</v>
       </c>
@@ -32335,6 +32458,9 @@
       <c r="M467" s="2">
         <v>769.27</v>
       </c>
+      <c r="N467" s="0">
+        <v>1</v>
+      </c>
       <c r="O467" s="0">
         <v>769.27</v>
       </c>
@@ -32388,6 +32514,9 @@
       <c r="M468" s="2">
         <v>769.27</v>
       </c>
+      <c r="N468" s="0">
+        <v>1</v>
+      </c>
       <c r="O468" s="0">
         <v>769.27</v>
       </c>
@@ -32441,6 +32570,9 @@
       <c r="M469" s="2">
         <v>-265.27</v>
       </c>
+      <c r="N469" s="0">
+        <v>1</v>
+      </c>
       <c r="O469" s="0">
         <v>-265.27</v>
       </c>
@@ -32494,6 +32626,9 @@
       <c r="M470" s="2">
         <v>-265.27</v>
       </c>
+      <c r="N470" s="0">
+        <v>1</v>
+      </c>
       <c r="O470" s="0">
         <v>-265.27</v>
       </c>
@@ -32547,6 +32682,9 @@
       <c r="M471" s="2">
         <v>80</v>
       </c>
+      <c r="N471" s="0">
+        <v>1</v>
+      </c>
       <c r="O471" s="0">
         <v>80</v>
       </c>
@@ -32600,6 +32738,9 @@
       <c r="M472" s="2">
         <v>80</v>
       </c>
+      <c r="N472" s="0">
+        <v>1</v>
+      </c>
       <c r="O472" s="0">
         <v>80</v>
       </c>
@@ -32653,6 +32794,9 @@
       <c r="M473" s="2">
         <v>-280.36</v>
       </c>
+      <c r="N473" s="0">
+        <v>1</v>
+      </c>
       <c r="O473" s="0">
         <v>-280.36</v>
       </c>
@@ -32706,6 +32850,9 @@
       <c r="M474" s="2">
         <v>-280.37</v>
       </c>
+      <c r="N474" s="0">
+        <v>1</v>
+      </c>
       <c r="O474" s="0">
         <v>-280.37</v>
       </c>
@@ -32759,6 +32906,9 @@
       <c r="M475" s="2">
         <v>498.71</v>
       </c>
+      <c r="N475" s="0">
+        <v>1</v>
+      </c>
       <c r="O475" s="0">
         <v>498.71</v>
       </c>
@@ -32812,6 +32962,9 @@
       <c r="M476" s="2">
         <v>498.71</v>
       </c>
+      <c r="N476" s="0">
+        <v>1</v>
+      </c>
       <c r="O476" s="0">
         <v>498.71</v>
       </c>
@@ -32865,8 +33018,11 @@
       <c r="M477" s="2">
         <v>925.01</v>
       </c>
+      <c r="N477" s="0">
+        <v>0.87058</v>
+      </c>
       <c r="O477" s="0">
-        <v>925.01</v>
+        <v>1062.52</v>
       </c>
       <c r="P477" s="0">
         <v>0</v>
@@ -32918,6 +33074,9 @@
       <c r="M478" s="2">
         <v>500.76</v>
       </c>
+      <c r="N478" s="0">
+        <v>1</v>
+      </c>
       <c r="O478" s="0">
         <v>500.76</v>
       </c>
@@ -32971,6 +33130,9 @@
       <c r="M479" s="2">
         <v>331.92</v>
       </c>
+      <c r="N479" s="0">
+        <v>1</v>
+      </c>
       <c r="O479" s="0">
         <v>331.92</v>
       </c>
@@ -33024,6 +33186,9 @@
       <c r="M480" s="2">
         <v>499.97</v>
       </c>
+      <c r="N480" s="0">
+        <v>1</v>
+      </c>
       <c r="O480" s="0">
         <v>499.97</v>
       </c>
@@ -33077,6 +33242,9 @@
       <c r="M481" s="2">
         <v>130</v>
       </c>
+      <c r="N481" s="0">
+        <v>1</v>
+      </c>
       <c r="O481" s="0">
         <v>130</v>
       </c>
@@ -33130,6 +33298,9 @@
       <c r="M482" s="2">
         <v>178.23</v>
       </c>
+      <c r="N482" s="0">
+        <v>1</v>
+      </c>
       <c r="O482" s="0">
         <v>178.23</v>
       </c>
@@ -33183,6 +33354,9 @@
       <c r="M483" s="2">
         <v>48.72</v>
       </c>
+      <c r="N483" s="0">
+        <v>1</v>
+      </c>
       <c r="O483" s="0">
         <v>48.72</v>
       </c>
@@ -33235,6 +33409,9 @@
       </c>
       <c r="M484" s="2">
         <v>-7.5</v>
+      </c>
+      <c r="N484" s="0">
+        <v>1</v>
       </c>
       <c r="O484" s="0">
         <v>-7.5</v>
